--- a/docs/Logic Requirements/Ageipelago Pachacuti.xlsx
+++ b/docs/Logic Requirements/Ageipelago Pachacuti.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{85BC8F20-E8D3-42BF-9F51-9BE506095DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59879C93-B296-4AD4-ADD6-9B206A4C76BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6AF541-8813-4371-937E-E9B91E747065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pachacuti" sheetId="1" r:id="rId1"/>
+    <sheet name="A New Power Arises" sheetId="2" r:id="rId2"/>
+    <sheet name="The Field of Blood" sheetId="3" r:id="rId3"/>
+    <sheet name="War of Brothers" sheetId="4" r:id="rId4"/>
+    <sheet name="The Falcon's Tent" sheetId="5" r:id="rId5"/>
+    <sheet name="Like Father, Like Son" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="211">
   <si>
     <t>Scenario</t>
   </si>
@@ -295,9 +300,519 @@
     </r>
   </si>
   <si>
+    <t>Starting Units:
+8 Kamayuks
+Urqu
+Viracocha</t>
+  </si>
+  <si>
+    <r>
+      <t>9 Villagers, 3 Town Centers, 1 Castle (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cuzco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+1000 Food, 1000 Wood, 1000 Gold, 600 Stone
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defend </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cuzco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> until the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wonder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is built
+Defend the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wonder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for 200 Years.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kill </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Urqu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kill </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Viracocha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Canchi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Chanca </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Player 6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Chanca </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Player 7)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ancco Hualloc
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/2/3/4/5/6/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>7/8/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castle/s</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Complete the Main Objectives with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> alive
+Complete the Main Objectives with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Canchi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> alive
+Complete the Main Objectives without constructing any Walls or Gates</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Beating the Mission without constructing any Walls or Gates is a Steam Achievement.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Urqu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Viracocha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> will leave the map early on, but if you try hard enough you can kill them before they get away.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kill </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Urqu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy the Castle
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Calas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hostile Inca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hostile Inca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chanca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Collect 1/2 Relic/s</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Inca Soldiers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> x8
+Reach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Inca Civilians</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> x5
+Destroy the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Siege Workshop</t>
+    </r>
+  </si>
+  <si>
+    <t>The Player needs to have optained the Monastery and Monk to collect the Relics.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Starting Units:
-10 Eagle Scouts
+Urqu
 </t>
     </r>
     <r>
@@ -321,11 +836,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
-5 Eagle Warriors
-8 Crossbowmen
-8 Kamayuks
-2 Battering Rams
+5 Kamayuks
 </t>
     </r>
     <r>
@@ -349,11 +860,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-4 Men-at-Arms
-5 Eagle Scouts
-6 Crossbowmen
-4 Kamayuks
-2 Battering Rams
+3 Kamayuks
 </t>
     </r>
     <r>
@@ -377,20 +884,427 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-11 Long Swordsmen
-3 Pikemen
-6 Eagle Warriors
-15 Crossbowmen
-8 Kamayuks
-12 Jaguar Warriors
-1 Mangonel
-3 Battering Rams</t>
-    </r>
+8 Kamayuks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/2/3/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castles
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Andahuaylas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Abancay</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kill </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anccu Hualloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Bring 8 Villagers to the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Priests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Colla</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9 Priests, 2 Relics (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Priests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Colla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> becomes an Ally</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Collect 1/2/3/4/5/6/7 Relic/s
+Destroy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castles
+Destroy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Wonders
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Priests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anccu Hualloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anccu Hualloc's Army</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Waman Karpa</t>
+    </r>
+  </si>
+  <si>
+    <t>The Player needs to have unlocked Monasteries and Monks to collect the Relics.</t>
+  </si>
+  <si>
+    <r>
+      <t>Kill 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Chieftain/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Bring 15 Military Units to the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wonder</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4 Villagers,1 Town Center, Misc. Units and Buildings (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pachacamac</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2 Monks, 1 Monastery (Gaia)
+2000 Food, 2000 Wood, 1500 Gold, 1500 Stone
+1200 Food, 950 Wood, 2000 Gold, 650 Stone
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chan Chan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> stops producing Champions, Elite Eagle Warriors, Arbalesters and Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <t>The Player needs to have optained or unlocked Monasteries and Monks to collect the Relics.
+The Player must have optained Villagers from Player 2 to proceed with other Objectives.</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>5 Villagers
+1 Town Center
+10 Champi Scouts
+Misc. Buildings
+400 Food
+650 Wood
+225 Gold
+250 Stone
+Technology: Fletching, Forging, Man-at-Arms (Standard)</t>
+  </si>
+  <si>
+    <t>Starting Units:
+2 Champi Scouts
+Later:
+10 Champi Warriors
+7 Crossbowmen
+3 Elite Skirmishers
+1 Battering Ram</t>
+  </si>
+  <si>
+    <t>Starting Units:
+2 Champi Scouts
+Later:
+16 Champi Warriors</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-1 Eagle Scout
+1 Champi Scout
 </t>
     </r>
     <r>
@@ -414,9 +1328,8 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
-6 Eagle Warriors
-9 Skirmishers
+3 Champi Warriors
+9 Elite Skirmishers
 6 Slingers
 2 Battering Rams
 2 Monks
@@ -443,9 +1356,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-4 Men-at-Arms
-6 Eagle Warriors
-6 Skirmishers
+6 Elite Skirmishers
 4 Slingers
 2 Battering Rams
 </t>
@@ -471,8 +1382,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-11 Long Swordsmen
-10 Eagle Warriors
+3 Champi Warriors
 12 Elite Skirmishers
 15 Slingers
 3 Scorpions
@@ -481,35 +1391,337 @@
     </r>
   </si>
   <si>
-    <t>According to the Wiki, Player 3 also trains Plumed Archers. I could not find anything in the AI-Script though.</t>
+    <r>
+      <t xml:space="preserve">Starting Units:
+11 Champi Scouts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+5 Elite Champi Warriors
+8 Crossbowmen
+8 Blackwood Archers
+2 Battering Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+5 Champi Warriors
+6 Crossbowmen
+4 Blackwood Archers
+2 Battering Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+6 Elite Champi Warriors
+3 Pikemen
+15 Crossbowmen
+12 Blackwood Archers
+1 Mangonel
+3 Battering Rams
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Guanaco</t>
+  </si>
+  <si>
+    <t>Tapir</t>
+  </si>
+  <si>
+    <t>Llama</t>
+  </si>
+  <si>
+    <t>Jaguar</t>
+  </si>
+  <si>
+    <t>Black Panther</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Champi Scout</t>
+  </si>
+  <si>
+    <t>Champi Runner</t>
+  </si>
+  <si>
+    <t>Champi Warrior</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Blackwood Archer</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pikeman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Champi Warrior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Slinger</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Only on hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Settlement</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Sea Tower</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Only Hard Logic</t>
+  </si>
+  <si>
+    <t>No Fire Galley
+No Galley
+No Hulk
+No Demolition Raft
+No Trade Cog</t>
+  </si>
+  <si>
+    <t>No Medium Warships
+No Demolition Ship
+On Standard, Fletching and Forging are researched automatically</t>
+  </si>
+  <si>
+    <t>14 Champi Runners
+6 Kamayuks
+10 Crossbowmen
+6 Elite Skirmishers
+1 Mangonel
+(inevitably die)
+Technology: Crossbowman, Elite Skirmisher, Champi Runner, Castle Age
+Technology: Fletching, Forging, Scale Mail Armor, Ballistics (Standard)</t>
   </si>
   <si>
     <t>Starting Units:
-2 Eagle Scouts
-Later:
-12 Men-at-Arms
-6 Eagle Scouts</t>
-  </si>
-  <si>
-    <t>Starting Units:
-2 Eagle Scouts
-Later:
-6 Long Swordsmen
-10 Eagle Warriors
-7 Crossbowmen
-3 Elite Skirmishers
-1 Battering Ram</t>
-  </si>
-  <si>
-    <t>Starting Units:
-8 Kamayuks
-Urqu
-Viracocha</t>
-  </si>
-  <si>
-    <t>Starting Units:
-6 Long Swordsmen
-24 Eagle Scouts
+6 Champi Runners
 7 Crossbowmen
 6 Slingers
 Cusi Yupanqui
@@ -517,403 +1729,27 @@
 Apo Mayta</t>
   </si>
   <si>
-    <r>
-      <t>9 Villagers, 3 Town Centers, 1 Castle (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cuzco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-1000 Food, 1000 Wood, 1000 Gold, 600 Stone
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defend </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cuzco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> until the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wonder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> is built
-Defend the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wonder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> for 200 Years.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kill </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Urqu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kill </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Viracocha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cana</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Canchi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Chanca </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Player 6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Chanca </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Player 7)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Ancco Hualloc
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2/3/4/5/6/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>7/8/9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Castle/s</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Complete the Main Objectives with </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cana</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> alive
-Complete the Main Objectives with </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Canchi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> alive
-Complete the Main Objectives without constructing any Walls or Gates</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6 Long Swordsmen, 24 Eagle Scouts, 7 Crossbowmen, 6 Slingers, Cusi Yupanqui, Vicaquirao, Apo Mayta (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cuzco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-Continuous Tribute x2</t>
-    </r>
-  </si>
-  <si>
     <t>Starting Units:
-7 Eagle Scouts
+1 Eagle Scout
+6 Champi Scouts
 1 Skirmisher
 Later:
-7 Eagle Warriors
+7 Champi Warriors
 7 Elite Skirmishers</t>
   </si>
   <si>
     <t>Starting Units:
-3 Men-at-Arms
+5 Champi Scouts
 6 Archers
 Later:
-7 Long Swordsmen
+7 Champi Warriors
 7 Crossbowmen</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beating the Mission without constructing any Walls or Gates is a Steam Achievement.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Urqu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Viracocha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> will leave the map early on, but if you try hard enough you can kill them before they get away.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Starting Units:
-10 Eagle Scouts
-4 Crossbowmen
+10 Champi Scouts
+5 Crossbowmen
 10 Slingers
 2 Scorpions
 </t>
@@ -939,8 +1775,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
-6 Eagle Warriors
+8 Champi Warriors
 9 Crossbowmen
 4 Slingers
 1 Mangonel
@@ -968,8 +1803,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-5 Long Swordsmen
-6 Eagle Scouts
+5 Champi Runners
 6 Crossbowmen
 3 Slingers
 2 Battering Rams
@@ -996,8 +1830,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-12 Long Swordsmen
-10 Eagle Warriors
+12 Champi Warriors
 12 Crossbowmen
 7 Slingers
 2 Mangonels
@@ -1007,7 +1840,7 @@
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-6 Eagle Scouts
+6 Champi Scouts
 6 Crossbowmen
 8 Elite Skirmishers
 1 Scorpion
@@ -1034,8 +1867,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
-6 Eagle Warriors
+8 Champi Warriors
 9 Elite Skirmishers
 4 Slingers
 1 Mangonel
@@ -1063,8 +1895,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-5 Long Swordsmen
-6 Eagle Scouts
+5 Champi Runners
 7 Elite Skirmishers
 3 Slingers
 4 Battering Rams
@@ -1091,8 +1922,7 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-12 Long Swordsmen
-10 Eagle Warriors
+12 Champi Warriors
 12 Elite Skirmishers
 7 Slingers
 2 Mangonels
@@ -1102,8 +1932,9 @@
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-10 Jaguar Warriors
+11 Champi Scouts
 5 Crossbowmen
+Addittional Crossbowmna, Champi Runners, Slingers and Elite Skirmishers, spawned until the Players troops are eliminated
 (despawn after initial Battle)
 </t>
     </r>
@@ -1196,63 +2027,130 @@
     </r>
   </si>
   <si>
-    <t>5 Villagers
-1 Town Center
-5 Eagle Scouts
-Misc. Buildings
-200 Food
-450 Wood
-225 Gold
-250 Stone
-Technology: Fletching, Forging, Man-at-Arms (Standard)</t>
-  </si>
-  <si>
-    <t>14 Eagle Scouts
-6 Kamayuks
-10 Crossbowmen
-6 Elite Skirmishers
-1 Mangonel
-(inevitably die)
-Technology: Crossbowman, Elite Skirmisher, Man-at-Arms, Castle Age
-Technology: Fletching, Forging, Scale Mail Armor, Ballistics (Standard)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kill </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Urqu</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy the Castle
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Calas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Champi Warrior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Elite Kamayuk</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Onager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Javelina</t>
+  </si>
+  <si>
+    <t>Kamayuk</t>
+  </si>
+  <si>
+    <t>Viracocha</t>
+  </si>
+  <si>
+    <t>Urqu</t>
+  </si>
+  <si>
+    <t>Only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Hut</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>Defeat Condition</t>
+  </si>
+  <si>
+    <t>Feudal - Imperial Age</t>
+  </si>
+  <si>
+    <r>
+      <t>6 Champi Runners, 7 Crossbowmen, 6 Slingers, Cusi Yupanqui, Vicaquirao, Apo Mayta (</t>
     </r>
     <r>
       <rPr>
@@ -1261,132 +2159,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Hostile Inca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hostile Inca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chanca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Collect 1/2 Relic/s</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Reach </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Inca Soldiers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> x8
-Reach </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Inca Civilians</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> x5
-Destroy the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Siege Workshop</t>
-    </r>
-  </si>
-  <si>
-    <t>The Player needs to have optained the Monastery and Monk to collect the Relics.</t>
-  </si>
-  <si>
-    <r>
-      <t>1 Eagle Scout, 3 Slingers, Misc. Buildings
-1 Crossbowman, 3 Elite Skirmishers, 1 Slinger, 1 Pavilion
-3 Eagle Scouts, 4 Crossbowmen, Misc. Buildings
-2 Eagle Scouts, 2 Elite Skirmishers, 3 Slingers, 2 Pavilions
-2 Eagle Scouts, 3 Crossbowmen, 2 Slingers, Misc. Buildings
-4 Petards, 1 Pavilion
-6 Eagle Scouts, 6 Crossbowmen, Misc. Buildings
-4 Eagle Scouts, 3 Crossbowmen, 3 Kamayuks, 1 Castle, Misc. Buildings
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Scattered Inca Army</t>
+      <t>Cuzco</t>
     </r>
     <r>
       <rPr>
@@ -1396,77 +2169,31 @@
         <family val="2"/>
       </rPr>
       <t>)
-6 Villagers, Misc. Buildings
-2 Villagers, Misc. Buildings x2
-4 Villagers, Misc. Buildings
-3 Villagers, Misc. Buildings
-1 Villagers, 1 Monk, Misc. Buildings
-2 Onagers, 3 Capped Rams
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Locals</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-The Player can build Siege Workshops
-The Player goptains Resources when destroying </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chanca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>'s Buildings</t>
-    </r>
-  </si>
-  <si>
-    <t>Starting Units:
-18 Eagle Scouts
-3 Kamayuks
-17 Crossbowmen
-5 Elite Skirmishers
-9 Slingers
-4 Petards</t>
-  </si>
-  <si>
-    <t>Starting Units:
-2 Onagers
-3 Capped Rams
-1 Monk</t>
-  </si>
-  <si>
-    <t>Starting Units:
-11 Eagle Scouts
-24 Jaguar Warriors
-24 Crossbowmen
-15 Elite Skirmishers</t>
-  </si>
-  <si>
-    <t>17 Eagle Scouts (Eagle Warriors on Standard)
+28 Champi Runners, 11 Slingers
+Continuous Tribute x2</t>
+    </r>
+  </si>
+  <si>
+    <t>No Docks</t>
+  </si>
+  <si>
+    <t>No Naval Units</t>
+  </si>
+  <si>
+    <t>Castle Age, Elite Skirmisher, Crossbowman and Champi Runnder are researched automatically
+On Standard Fletching, Forging, Ballistics and Scale Mail Armor are researched automatically
+No Dock Techs
+No Careening
+No Clinker Construction
+No Dry Dock
+No Shipwright
+No Spies</t>
+  </si>
+  <si>
+    <t>Cusi Yupanqui</t>
+  </si>
+  <si>
+    <t>18 Champi Scouts (Champi Warriors on Standard)
 6 Kamayuks
 4 Crossbowmen
 4 Elite Skirmishers
@@ -1480,182 +2207,8 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
-20 Spearmen
-38 Eagle Scouts
-7 Eagle Warriors
-25 Crossbowmen
-30 Skirmishers
-14 Slingers
-24 Plumed Archers
-3 Scorpions
-2 Mangonels
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
-20 Spearmen
-33 Eagle Scouts
-5 Eagle Warriors
-25 Crossbowmen
-30 Skirmishers
-14 Slingers
-21 Plumed Archers
-2 Scorpions
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
-20 Pikemen
-38 Eagle Scouts
-7 Eagle Warriors
-25 Crossbowmen
-30 Elite Skirmishers
-14 Slingers
-24 Plumed Archers
-3 Scorpions
-2 Mangonels</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Starting Units:
-Urqu
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-5 Kamayuks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-3 Kamayuks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Kamayuks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-3 Eagle Scouts
+3 Champi Warriors
 9 Crossbowmen
 2 Mangonels
 </t>
@@ -1681,7 +2234,6 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
 9 Crossbowmen
 4 Slingers
 1 Mangonel
@@ -1708,7 +2260,6 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-5 Long Swordsmen
 6 Crossbowmen
 3 Slingers
 </t>
@@ -1734,16 +2285,36 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-12 Long Swordsmen
 12 Crossbowmen
 7 Slingers
 2 Mangonels</t>
     </r>
   </si>
   <si>
+    <t>Starting Units:
+2 Onagers
+2 Capped Rams
+1 Monk</t>
+  </si>
+  <si>
+    <t>Starting Units:
+16 Champi Scouts
+3 Champi Warriors
+3 Kamayuks
+17 Crossbowmen
+7 Elite Skirmishers
+11 Slingers
+2 Saboteurs</t>
+  </si>
+  <si>
+    <t>Starting Units:
+29 Champi Scouts
+21 Blackwood Archers
+15 Elite Skirmishers</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Starting Units:
-3 Eagle Scouts
 3 Crossbowmen
 </t>
     </r>
@@ -1768,11 +2339,575 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Long Swordsmen
-2 Eagle Warrior
+5 Champi Warriors
+5 Crossbowmen
+3 Slingers
+1 Mangonel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+3 Champi Warriors
+3 Crossbowmen
+2 Slingers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+7 Champi Warriors
+7 Crossbowmen
+5 Slingers
+2 Mangonels</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3 Slingers, 1 Chambi Scout
+1 Crossbowman, 3 Elite Skirmishers, 1 Slinger
+4 Crossbowmen, 3 Champi Warriors
+3 Crossbowmen, 2 Slingers, 2 Champi Scouts
+2 Elite Skirmishers, 2 Slingers, 2 Champi Scouts
+2 Elite Skirmishers, 3 Slingers, 2 Champi Scouts
+3 Crossbowmen, 3 Champi Scouts, Misc. Buildings
+3 Kamayuks, 1 Castle
+6 Crossbowmen, 6 Champi Runners, Misc. Buildings
+2 Saboteurs
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scattered Inca Soldiers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+6 Villagers, Misc. Buildings
+2 Villagers, Misc. Buildings x2
+4 Villagers, Misc. Buildings
+3 Villagers, Misc. Buildings
+1 Villagers, 1 Monk, Misc. Buildings
+2 Onagers, 3 Capped Rams
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Locals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+The Player can build Siege Workshops
+The Player goptains Resources when destroying </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chanca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>'s Buildings</t>
+    </r>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+20 Spearmen
+56 Champi Runners
+25 Crossbowmen
+46 Skirmishers
+28 Slingers
+4 Scorpions
+2 Mangonels
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+20 Spearmen
+48 Champi Runners
+25 Crossbowmen
+46 Skirmishers
+28 Slingers
+2 Scorpions
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+20 Pikemen
+56 Champi Runners
+25 Crossbowmen
+46 Elite Skirmishers
+28 Slingers
+4 Scorpions
+2 Mangonels</t>
+    </r>
+  </si>
+  <si>
+    <t>Black Bear</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>Hut (Large)</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>House
+Settlement
+Farm
+Outpost
+Watch Tower
+Guard Tower</t>
+  </si>
+  <si>
+    <t>Champi Runner
+Champi Warrior
+Spearman
+Pikeman
+Archer
+Skirmisher
+Slinger
+Crossbowman
+Elite Skirmisher
+Monk
+Fishing Ship
+Transport Ship
+Kamayuk
+Petard</t>
+  </si>
+  <si>
+    <t>Horse Collar
+Double-Bit Axe
+Stone Mining
+Gold Mining
+Heavy Plow
+Bow Saw
+Stone Shaft Mining
+Gold Shaft Mining
+Crossbowman
+Elite Skirmisher
+Thumb Ring
+Champi Warrior
+Pikeman
+Arson
+Squires
+Devotion
+Sanctity
+Heresy
+Herbal Medicine
+Fishing Lines
+Gillnets
+Masonry
+Murder Holes
+Heated Shot
+Ballistics
+Guard Tower
+Treadmill Crane
+Andean Sling
+Fletching
+Bodkin Arrow
+Forging
+Scale Mail Armor
+Padded Archer Armor
+Leather Archer Armor
+Chain Mail Armor
+Iron Casting
+On Standard Forging, Fletching, Wheelbarrow, Capped Ram and Siege Ram are researched automatically</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+4 Champi Scouts
+2 Monks
+2 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Elite Champi Warriors
+11 Elite Blackwood Archers
+10 Arbalests
+1 Mangonel
+2 Battering Rams
+2 Trebuchets
+2 Monks
+4 War Galleys
+2 Fire Ships
+2 Demolition Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Champi Warriors
+9  Blackwood Archers
 9 Crossbowmen
+1 Battering Ram
+4 War Galleys
+2 Fire Ships
+2 Demolition Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+14 Elite Champi Warriors
+14 Elite Blackwood Archers
+12 Arbalests
+3 Mangonels
+2 Battering Rams
+2 Trebuchets
+2 Monks
+5 War Galleys
+2 Fire Ships
+2 Demolition Ships</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+1 Champi Scout
+6 Slingers
+1 War Galley
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+12 Champi Warriors
+5 Blackwood Archers
+13 Elite Skirmishers
+10 Slingers
+4 Scorpions
+1 Battering Ram
+1 Trebuchet
+5 War Galleys
+2 Fire Ships
+2 Demolition Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+8 Champi Warriors
+3 Blackwood Archers
+10 Skirmishers
+9 Slingers
+2 Scorpions
+1 Battering Ram
+1 Trebuchet
+4 War Galleys
+2 Fire Ships
+2 Demolition Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+15 Champi Warriors
+7 Blackwood Archers
+15 Elite Skirmishers
+12 Slingers
+4 Scorpions
+2 Battering Rams
+1 Trebuchet
+7 War Galleys
+2 Fire Ships
+2 Demolition Ships</t>
+    </r>
+  </si>
+  <si>
+    <t>Starting Units:
+12 Champi Scouts
+Anccu Hualloc</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+47 Campi Scouts
+3 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+8 Champi Warriors
+8 Arbalests
+4 Elite Blackwood Archers
 4 Slingers
 1 Mangonel
+1 Trebuchet
+4 War Galleys
+2 Fire Ships
 </t>
     </r>
     <r>
@@ -1796,9 +2931,13 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-5 Long Swordsmen
-6 Crossbowmen
+5 Champi Warriors
+5 Crossbowmen
+3 Blackwood Archers
 3 Slingers
+1 Mangonel
+4 War Galleys
+1 Fire Ship
 </t>
     </r>
     <r>
@@ -1822,36 +2961,91 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-12 Long Swordsmen
-2 Eagle Warrior
-12 Crossbowmen
+11 Elite Champi Warriors
+10 Arbalests
+7 Elite Blackwood Archers
 7 Slingers
-2 Mangonels</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2/3/4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Castles
-Defeat </t>
-    </r>
+2 Mangonels
+1 Trebuchet
+5 War Galleys
+2 Fire Ships</t>
+    </r>
+  </si>
+  <si>
+    <t>Starting Units:
+8 Temple Guards
+2 Elite Temple Guards
+28 Elite Gueacha Warriors
+21 Slingers
+8 Onagers</t>
+  </si>
+  <si>
+    <t>Starting Units:
+4 Monks
+1 Priest</t>
+  </si>
+  <si>
+    <t>Caiman</t>
+  </si>
+  <si>
+    <t>Crocodile</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Arbalester</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Blackwood Archer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Anccu Hualloc</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="14"/>
@@ -1859,18 +3053,118 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Andahuaylas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
+      <t>Elite Skirmisher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+23 Champi Scouts
+3 Mangonels
+1 Monk
+1 War Galley
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+12 Halberdiers
+15 Elite Champi Warriors
+12 Arbalests
+2 Onagers
+3 War Galleys
+4 Fire Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+9 Pikemen
+15 Champi Warriors
+9 Crossbowmen
+1 Onager
+4 War Galleys
+1 Fire Ship
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+15 Halberdiers
+20 Elite Champi Warriors
+16 Arbalests
+3 Onagers
+4 War Galleys
+3 Fire Ships</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Champi Warrior</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="14"/>
@@ -1878,123 +3172,48 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Abancay</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kill </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Anccu Hualloc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Bring 8 Villagers to the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Priests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Reach </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colla</t>
-    </r>
-  </si>
-  <si>
-    <t>Starting Units:
-9 Priests</t>
-  </si>
-  <si>
-    <r>
-      <t>9 Priests, 2 Relics (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Priests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Starting Units:
-6 Kamayuks
-18 Jaguar Warriors
-14 Slingers
-8 Onagers</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Colla</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> becomes an Ally</t>
-    </r>
-  </si>
-  <si>
-    <t>Starting Units:
-6 Elite Jaguar Warriors
-Anccu Hualloc</t>
+      <t>Elite Champi Warrior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Priest</t>
+  </si>
+  <si>
+    <t>Temple Guard</t>
+  </si>
+  <si>
+    <t>Elite Temple Guard</t>
+  </si>
+  <si>
+    <t>Elite Guecha Warrior</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
   </si>
   <si>
     <t>8 Villagers
-9 Eagle Warriors
+13 Champi Scouts
 9 Kamayuks
 9 Crossbowmen
 9 Elite Skirmishers
@@ -2007,9 +3226,53 @@
 (+500 of every Resource on Standard)</t>
   </si>
   <si>
-    <r>
-      <t>Collect 1/2/3/4/5/6/7 Relic/s
-Destroy</t>
+    <t>No Wonder</t>
+  </si>
+  <si>
+    <t>No Spies
+On Standard Siege Engineers and Arbalest are researched automatically</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chimú Navy's Market</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chimú Army</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
     </r>
     <r>
       <rPr>
@@ -2018,73 +3281,17 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 1/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Castles
-Destroy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Wonders
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Priests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
+      <t>Chimú Skirmishers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
     </r>
     <r>
       <rPr>
@@ -2093,565 +3300,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Anccu Hualloc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Anccu Hualloc's Army</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Waman Karpa</t>
-    </r>
-  </si>
-  <si>
-    <t>The Player needs to have unlocked Monasteries and Monks to collect the Relics.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-2 Eagle Warriors
-47 Jaguar Warriors
-3 War Galleys
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Two-Handed Swordsmen
-1 Eagle Warrior
-8 Arbalests
-4 Slingers
-1 Mangonel
-1 Trebuchet
-4 War Galleys
-2 Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-5 Two-Handed Swordsmen
-1 Eagle Warrior
-5 Crossbowmen
-3 Slingers
-1 Mangonel
-4 War Galleys
-1 Fire Ship
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-11 Champions
-1 Eagle Warrior
-10 Arbalests
-7 Slingers
-2 Mangonels
-1 Trebuchet
-5 War Galleys
-2 Fire Ships</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-12 Eagle Warriors
-3 Mangonels
-1 Monk
-1 War Galley
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-12 Halberdiers
-8 Elite Eagle Warriors
-12 Arbalests
-2 Onagers
-3 War Galleys
-4 Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-9 Pikemen
-8 Eagle Warriors
-9 Crossbowmen
-1 Onager
-4 War Galleys
-1 Fire Ship
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-15 Halberdiers
-12 Elite Eagle Warriors
-16 Arbalests
-3 Onagers
-4 War Galleys
-3 Fire Ships</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-2 Eagle Scouts
-6 Slingers
-1 War Galley
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-12 Two-Handed Swordsmen
-6 Elite Eagle Warriors
-5 Kamayuks
-9 Elite Skirmishers
-10 Slingers
-4 Scorpions
-1 Battering Ram
-1 Trebuchet
-5 War Galleys
-2 Fire Ships
-2 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Long Swordsmen
-6 Eagle Warriors
-3 Kamayuks
-6 Skirmishers
-9 Slingers
-2 Scorpions
-1 Battering Ram
-1 Trebuchet
-4 War Galleys
-2 Fire Ships
-2 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-15 Two-Handed Swordsmen
-10 Elite Eagle Warriors
-7 Kamayuks
-12 Elite Skirmishers
-12 Slingers
-4 Scorpions
-2 Battering Rams
-1 Trebuchet
-7 War Galleys
-2 Fire Ships
-2 Demolition Ships</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-4 Eagle Warriors
-2 Monks
-2 War Galleys
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Champions
-10 Elite Eagle Warriors
-11 Elite Kamayuks
-10 Arbalests
-1 Mangonel
-2 Battering Rams
-2 Trebuchets
-2 Monks
-4 War Galleys
-2 Fire Ships
-2 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-4 Two-Handed Swordsmen
-10 Eagle Warriors
-9  Kamayuks
-9 Crossbowmen
-1 Battering Ram
-4 War Galleys
-2 Fire Ships
-2 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-10 Champions
-14 Elite Eagle Warriors
-14 Elite Kamayuks
-12 Arbalests
-3 Mangonels
-2 Battering Rams
-2 Trebuchets
-2 Monks
-5 War Galleys
-2 Fire Ships
-2 Demolition Ships</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kill 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Chieftain/s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Bring 15 Military Units to the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wonder</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chimú Navy's Market</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chimú Army</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chimú Army</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chimú Army</t>
+      <t>Chimú Vanguard</t>
     </r>
   </si>
   <si>
@@ -2672,11 +3321,29 @@
     <r>
       <rPr>
         <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>7/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>8/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
         <color rgb="FFFFC000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>7/8/9</t>
+      <t>9</t>
     </r>
     <r>
       <rPr>
@@ -2746,56 +3413,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>4 Villagers,1 Town Center, Misc. Units and Buildings (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pachacamac</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2 Monks, 1 Monastery (Gaia)
-2000 Food, 2000 Wood, 1500 Gold, 1500 Stone
-1200 Food, 950 Wood, 2000 Gold, 650 Stone
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chan Chan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> stops producing Champions, Elite Eagle Warriors, Arbalesters and Trebuchets</t>
-    </r>
-  </si>
-  <si>
-    <t>4 Eagle Warriors
+    <t>4 Champi Scouts
 20 Kamayuks
 20 Crossbowmen
 10 Elite Skrmishers
@@ -2808,15 +3426,10 @@
 Technology: Arbalester, Galleon, Heavy Scorpion (Only on Standard)</t>
   </si>
   <si>
-    <t>The Player needs to have optained or unlocked Monasteries and Monks to collect the Relics.
-The Player must have optained Villagers from Player 2 to proceed with other Objectives.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Starting Units:
-9 Two-Handed Swordsmen
-4 Eagle Warriors
-20 Plumed Archers
+18 Champi Scouts
+28 Blackwood Archers
 4 Chieftains
 3 Mangonels
 </t>
@@ -2843,7 +3456,7 @@
       <t xml:space="preserve">
 Later:
 2 Crossbowmen
-1 Pikeman
+3 Champi Scouts
 </t>
     </r>
     <r>
@@ -2868,6 +3481,7 @@
       <t xml:space="preserve">
 Later:
 1 Crossbowman
+2 Champi Scouts
 </t>
     </r>
     <r>
@@ -2892,13 +3506,13 @@
       <t xml:space="preserve">
 Later:
 2 Crossbowmen
-2 Pikemen</t>
+4 Champi Scouts</t>
     </r>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-6 Eagle Warriors
+6 Champi Scouts
 </t>
     </r>
     <r>
@@ -2922,9 +3536,9 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Later:
-8 Champions
-10 Elite Eagle Warriors
-10 Elite Kamayuks
+10 Elite Champi Warriors
+8 Elite Temple Guards
+10 Elite Guecha Warriors
 2 Arbalesters
 9 Elite Skirmishers
 1 Trebuchet
@@ -2951,9 +3565,9 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-4 Two-Handed Swordsmen
-10 Eagle Warriors
-7 Kamayuks
+10 Champi Warriors
+4 Temple Guards
+7 Guecha Warriors
 5 Elite Skirmishers
 1 Trebuchet
 </t>
@@ -2979,9 +3593,9 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-11 Champions
-14 Elite Eagle Warriors
-12 Elite Kamayuks
+14 Elite Champi Warriors
+11 Elite Temple Guards
+12 Elite Guecha Warriors
 2 Arbalesters
 12 Elite Skirmishers
 2 Trebuchets</t>
@@ -2990,8 +3604,8 @@
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-2 Eagle Warriors
-2 Mangonels
+2 Champi Scouts
+8 Arbalesters
 </t>
     </r>
     <r>
@@ -3015,9 +3629,8 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Champions
-2 Eagle Warriors
-8 Arbalesters
+10 Elite Champi Warriors
+12 Arbalesters
 4 Slingers
 2 Mangonels
 </t>
@@ -3043,8 +3656,8 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-5 Champions
-6 Arbalesters
+6 Elite Champi Warriors
+9 Arbalesters
 3 Slingers
 1 Mangonel
 </t>
@@ -3070,15 +3683,18 @@
       </rPr>
       <t xml:space="preserve">
 Later:
-8 Champions
-2 Eagle Warriors
-9 Arbalesters
+10 Elite Champi Warriors
+16 Arbalesters
 7 Slingers
 2 Mangonels</t>
     </r>
   </si>
   <si>
     <r>
+      <t>8 Slingers
+2 Scorpions</t>
+    </r>
+    <r>
       <rPr>
         <b/>
         <sz val="14"/>
@@ -3087,21 +3703,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-8 Champions
-2 Eagle Warriors
+      <t xml:space="preserve">
+Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+8 Elite Champi Warriors
 8 Arbalesters
-4 Slingers
+20 Slingers
 2 Scorpions
 1 Trebuchet
 </t>
@@ -3126,9 +3742,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-5 Champions
-4 Arbalesters
-3 Slingers
+5 Elite Champi Warriors
+16 Slingers
 1 Scorpion
 </t>
     </r>
@@ -3152,16 +3767,21 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-10 Champions
-2 Eagle Warriors
+10 Elite Champi Warriors
 9 Arbalesters
-6 Slingers
+25 Slingers
 3 Scorpions
 1 Trebuchet</t>
     </r>
   </si>
   <si>
     <r>
+      <t xml:space="preserve">14 Champi Scouts
+9 Elite Skirmishers
+2 Onagers
+</t>
+    </r>
+    <r>
       <rPr>
         <b/>
         <sz val="14"/>
@@ -3181,10 +3801,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-7 Champions
-2 Eagle Warriors
-8 Arbalesters
-4 Slingers
+15 Elite Skirmishers
+2 Onagers
 1 Battering Ram
 1 Trebuchet
 </t>
@@ -3209,10 +3827,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-4 Champions
-2 Eagle Warriors
-5 Arbalesters
-3 Slingers
+12 Elite Skirmishers
+1 Onager
 1 Trebuchet
 </t>
     </r>
@@ -3236,10 +3852,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-8 Champions
-2 Eagle Warriors
-10 Arbalesters
-7 Slingers
+17 Elite Skirmishers
+2 Onagers
 2 Battering Rams
 1 Trebuchet</t>
     </r>
@@ -3265,11 +3879,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-7 Champions
-7 Eagle Warriors
+14 Elite Champi Warriors
 5 Galleons
-3 Fire Ships
-1 Demolition Ship
+2 Fire Ships
+1 War Hulk
 </t>
     </r>
     <r>
@@ -3292,11 +3905,9 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-4 Champions
-4 Eagle Warriors
+8 Elite Champi Warriors
 3 Galleons
-3 Fire Ships
-1 Demolition Ship
+2 Fire Ships
 </t>
     </r>
     <r>
@@ -3319,19 +3930,103 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-10 Champions
-10 Eagle Warriors
+20 Elite Champi Warriors
 5 Galleons
-3 Fire Ships
-1 Demolition Ship</t>
-    </r>
+2 Fire Ships
+1 War Hulk</t>
+    </r>
+  </si>
+  <si>
+    <t>Chieftain</t>
+  </si>
+  <si>
+    <t>Guecha Warrior</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Guecha Warrior
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Temple Guard
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>War Hulk</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Requires Dock or Trebuchet</t>
+  </si>
+  <si>
+    <t>Cistern (Aqueduct)</t>
+  </si>
+  <si>
+    <t>Cistern (City Wall)</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Halberdier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>No Spies
+Siege Engineers is researched automatically
+On Moderate and Standard, Bracer is researched automatically
+On Standard, Arbalester, Galleon and Heavy Scorpion are researched automatically</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3444,6 +4139,81 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3453,7 +4223,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3541,11 +4311,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3590,6 +4432,141 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3982,26 +4959,24 @@
         <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -4013,46 +4988,46 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="Q5" s="7"/>
     </row>
@@ -4061,45 +5036,45 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="7" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4107,47 +5082,47 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="7" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4155,45 +5130,45 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="7" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4272,4 +5247,2658 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B18A8E8-8F50-4711-90C9-72C87F282F2B}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="G6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="G7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="G8" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="G10" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="G11" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="G12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="G13" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="G14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="G15" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="G16" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1042B617-A2BB-4F13-BCBE-559B072875E8}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="356.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="G6" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="G7" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="G8" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="G10" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="G11" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="G12" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="G13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="G14" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="G15" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="G16" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K24" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0773C01D-842D-484D-9EE3-4B28C374F656}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="G6" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="G7" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="G8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="G10" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="G11" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="G12" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="G13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="G14" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="G15" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="G16" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="K22" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321C1A9C-42B9-41EC-864A-5632884A9890}">
+  <dimension ref="B1:L43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="G6" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="G7" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="G8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="G10" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="G11" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="G12" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="G13" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="G14" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="G15" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="G16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G17" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G31" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G34" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G38" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC97C48-E6E7-4156-952E-F41BDC294DDD}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="262.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="G6" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="G7" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="G8" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="G9" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="G10" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="G11" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="G12" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="G13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="48"/>
+      <c r="G14" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="48"/>
+      <c r="G15" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="48"/>
+      <c r="G16" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="4:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="D17" s="48"/>
+      <c r="G17" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D18" s="48"/>
+      <c r="G18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="D19" s="48"/>
+      <c r="G19" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+    </row>
+    <row r="30" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+    </row>
+    <row r="32" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>